--- a/Data/EXCEL/Transfer/salemon/20240711/6462-salemon-20240711.xlsx
+++ b/Data/EXCEL/Transfer/salemon/20240711/6462-salemon-20240711.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlsx\20240711\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\GithubProjects\GoodinfoData2DB\Data\EXCEL\Transfer\salemon\20240711\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F71D9737-A255-478B-800F-E45E30597568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DEB91CC2-1526-4656-BE37-8E5B692979C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="290" windowWidth="18240" windowHeight="13390" xr2:uid="{CA4779EB-B10D-4C7B-94DB-7D1B9E8401BF}"/>
+    <workbookView xWindow="768" yWindow="684" windowWidth="20004" windowHeight="13956" xr2:uid="{A0AF28E2-378E-4ECA-8ABF-000F7ADF8CCD}"/>
   </bookViews>
   <sheets>
     <sheet name="6462-salemon-20240711" sheetId="2" r:id="rId1"/>
@@ -1261,16 +1261,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0E26F07-2F6B-4841-B0BA-D61DE26A6532}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FC6BBE9-D939-4EF5-BFF5-CD50FDF9B7DB}">
   <dimension ref="A1:Q257"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="6" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="17" width="6.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="6" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="17" width="6.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -1297,7 +1297,7 @@
       <c r="P1" s="19"/>
       <c r="Q1" s="20"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="16"/>
       <c r="B2" s="15" t="s">
         <v>4</v>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="16"/>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
@@ -1379,7 +1379,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -1418,7 +1418,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>45444</v>
       </c>
@@ -1471,7 +1471,7 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="10">
         <v>45413</v>
       </c>
@@ -1524,7 +1524,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>45383</v>
       </c>
@@ -1577,7 +1577,7 @@
         <v>8.73</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="10">
         <v>45352</v>
       </c>
@@ -1630,7 +1630,7 @@
         <v>9.31</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>45323</v>
       </c>
@@ -1683,7 +1683,7 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="10">
         <v>45292</v>
       </c>
@@ -1736,7 +1736,7 @@
         <v>48.1</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>45261</v>
       </c>
@@ -1789,7 +1789,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="10">
         <v>45231</v>
       </c>
@@ -1842,7 +1842,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>45200</v>
       </c>
@@ -1895,7 +1895,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="10">
         <v>45170</v>
       </c>
@@ -1948,7 +1948,7 @@
         <v>11.4</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>45139</v>
       </c>
@@ -2001,7 +2001,7 @@
         <v>8.93</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="10">
         <v>45108</v>
       </c>
@@ -2054,7 +2054,7 @@
         <v>8.34</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>45078</v>
       </c>
@@ -2107,7 +2107,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="10">
         <v>45047</v>
       </c>
@@ -2160,7 +2160,7 @@
         <v>-0.49</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>45017</v>
       </c>
@@ -2213,7 +2213,7 @@
         <v>-6.21</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="10">
         <v>44986</v>
       </c>
@@ -2266,7 +2266,7 @@
         <v>1.36</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>44958</v>
       </c>
@@ -2319,7 +2319,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="10">
         <v>44927</v>
       </c>
@@ -2372,7 +2372,7 @@
         <v>-11.1</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>44896</v>
       </c>
@@ -2425,7 +2425,7 @@
         <v>-4.45</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="10">
         <v>44866</v>
       </c>
@@ -2478,7 +2478,7 @@
         <v>-3.82</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>44835</v>
       </c>
@@ -2531,7 +2531,7 @@
         <v>-5.5</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>44805</v>
       </c>
@@ -2584,7 +2584,7 @@
         <v>-7.15</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>44774</v>
       </c>
@@ -2637,7 +2637,7 @@
         <v>-1.41</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="10">
         <v>44743</v>
       </c>
@@ -2690,7 +2690,7 @@
         <v>-1.97</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>44713</v>
       </c>
@@ -2743,7 +2743,7 @@
         <v>-9.24</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>44682</v>
       </c>
@@ -2796,7 +2796,7 @@
         <v>-8.42</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
         <v>44652</v>
       </c>
@@ -2849,7 +2849,7 @@
         <v>-10.6</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>44621</v>
       </c>
@@ -2902,7 +2902,7 @@
         <v>-15.4</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>44593</v>
       </c>
@@ -2955,7 +2955,7 @@
         <v>-28.2</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>44562</v>
       </c>
@@ -3008,7 +3008,7 @@
         <v>-15.2</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>44531</v>
       </c>
@@ -3061,7 +3061,7 @@
         <v>-44.7</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>44501</v>
       </c>
@@ -3114,7 +3114,7 @@
         <v>-48.2</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>44470</v>
       </c>
@@ -3167,7 +3167,7 @@
         <v>-48.6</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>44440</v>
       </c>
@@ -3220,7 +3220,7 @@
         <v>-47.6</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
         <v>44409</v>
       </c>
@@ -3273,7 +3273,7 @@
         <v>-49.8</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>44378</v>
       </c>
@@ -3326,7 +3326,7 @@
         <v>-47.5</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>44348</v>
       </c>
@@ -3379,7 +3379,7 @@
         <v>-42.8</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>44317</v>
       </c>
@@ -3432,7 +3432,7 @@
         <v>-38.5</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" s="5">
         <v>44287</v>
       </c>
@@ -3485,7 +3485,7 @@
         <v>-34.700000000000003</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>44256</v>
       </c>
@@ -3538,7 +3538,7 @@
         <v>-34.6</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" s="5">
         <v>44228</v>
       </c>
@@ -3591,7 +3591,7 @@
         <v>-27.5</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>44197</v>
       </c>
@@ -3644,7 +3644,7 @@
         <v>-38.1</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" s="5">
         <v>44166</v>
       </c>
@@ -3697,7 +3697,7 @@
         <v>-15.4</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>44136</v>
       </c>
@@ -3750,7 +3750,7 @@
         <v>-10.5</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" s="5">
         <v>44105</v>
       </c>
@@ -3803,7 +3803,7 @@
         <v>-10.3</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" s="10">
         <v>44075</v>
       </c>
@@ -3856,7 +3856,7 @@
         <v>-6.35</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" s="5">
         <v>44044</v>
       </c>
@@ -3909,7 +3909,7 @@
         <v>-2.58</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" s="10">
         <v>44013</v>
       </c>
@@ -3962,7 +3962,7 @@
         <v>-2.36</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" s="5">
         <v>43983</v>
       </c>
@@ -4015,7 +4015,7 @@
         <v>-3.59</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" s="10">
         <v>43952</v>
       </c>
@@ -4068,7 +4068,7 @@
         <v>-0.27</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" s="5">
         <v>43922</v>
       </c>
@@ -4121,7 +4121,7 @@
         <v>8.19</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" s="10">
         <v>43891</v>
       </c>
@@ -4174,7 +4174,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" s="5">
         <v>43862</v>
       </c>
@@ -4227,7 +4227,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" s="10">
         <v>43831</v>
       </c>
@@ -4280,7 +4280,7 @@
         <v>38.4</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" s="5">
         <v>43800</v>
       </c>
@@ -4333,7 +4333,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" s="10">
         <v>43770</v>
       </c>
@@ -4386,7 +4386,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" s="5">
         <v>43739</v>
       </c>
@@ -4439,7 +4439,7 @@
         <v>18.8</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" s="10">
         <v>43709</v>
       </c>
@@ -4492,7 +4492,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" s="5">
         <v>43678</v>
       </c>
@@ -4545,7 +4545,7 @@
         <v>7.22</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" s="10">
         <v>43647</v>
       </c>
@@ -4598,7 +4598,7 @@
         <v>5.84</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" s="5">
         <v>43617</v>
       </c>
@@ -4651,7 +4651,7 @@
         <v>5.72</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" s="10">
         <v>43586</v>
       </c>
@@ -4704,7 +4704,7 @@
         <v>3.01</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" s="5">
         <v>43556</v>
       </c>
@@ -4757,7 +4757,7 @@
         <v>-4.29</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" s="10">
         <v>43525</v>
       </c>
@@ -4810,7 +4810,7 @@
         <v>-14.7</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" s="5">
         <v>43497</v>
       </c>
@@ -4863,7 +4863,7 @@
         <v>-29</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" s="10">
         <v>43466</v>
       </c>
@@ -4916,7 +4916,7 @@
         <v>-43.1</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" s="5">
         <v>43435</v>
       </c>
@@ -4969,7 +4969,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" s="10">
         <v>43405</v>
       </c>
@@ -5022,7 +5022,7 @@
         <v>34.1</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" s="5">
         <v>43374</v>
       </c>
@@ -5075,7 +5075,7 @@
         <v>35.299999999999997</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" s="10">
         <v>43344</v>
       </c>
@@ -5128,7 +5128,7 @@
         <v>35.299999999999997</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" s="5">
         <v>43313</v>
       </c>
@@ -5181,7 +5181,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" s="10">
         <v>43282</v>
       </c>
@@ -5234,7 +5234,7 @@
         <v>45.6</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" s="5">
         <v>43252</v>
       </c>
@@ -5287,7 +5287,7 @@
         <v>51.1</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" s="10">
         <v>43221</v>
       </c>
@@ -5340,7 +5340,7 @@
         <v>48.2</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" s="5">
         <v>43191</v>
       </c>
@@ -5393,7 +5393,7 @@
         <v>39.299999999999997</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" s="10">
         <v>43160</v>
       </c>
@@ -5446,7 +5446,7 @@
         <v>37.799999999999997</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" s="5">
         <v>43132</v>
       </c>
@@ -5499,7 +5499,7 @@
         <v>31.4</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" s="10">
         <v>43101</v>
       </c>
@@ -5552,7 +5552,7 @@
         <v>50.2</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A83" s="5">
         <v>43070</v>
       </c>
@@ -5605,7 +5605,7 @@
         <v>182.8</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A84" s="10">
         <v>43040</v>
       </c>
@@ -5658,7 +5658,7 @@
         <v>214.1</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85" s="5">
         <v>43009</v>
       </c>
@@ -5711,7 +5711,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" s="10">
         <v>42979</v>
       </c>
@@ -5764,7 +5764,7 @@
         <v>340.8</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87" s="5">
         <v>42948</v>
       </c>
@@ -5817,7 +5817,7 @@
         <v>380.9</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A88" s="10">
         <v>42917</v>
       </c>
@@ -5870,7 +5870,7 @@
         <v>454.6</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" s="5">
         <v>42887</v>
       </c>
@@ -5923,7 +5923,7 @@
         <v>474.7</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A90" s="10">
         <v>42856</v>
       </c>
@@ -5976,7 +5976,7 @@
         <v>444.4</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" s="5">
         <v>42826</v>
       </c>
@@ -6029,7 +6029,7 @@
         <v>859.2</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A92" s="10">
         <v>42795</v>
       </c>
@@ -6082,7 +6082,7 @@
         <v>1016.3</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A93" s="5">
         <v>42767</v>
       </c>
@@ -6135,7 +6135,7 @@
         <v>826.1</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A94" s="10">
         <v>42736</v>
       </c>
@@ -6188,7 +6188,7 @@
         <v>2406.1999999999998</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A95" s="5">
         <v>42705</v>
       </c>
@@ -6241,7 +6241,7 @@
         <v>213.1</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A96" s="10">
         <v>42675</v>
       </c>
@@ -6294,7 +6294,7 @@
         <v>179.1</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A97" s="5">
         <v>42644</v>
       </c>
@@ -6347,7 +6347,7 @@
         <v>188.4</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A98" s="10">
         <v>42614</v>
       </c>
@@ -6400,7 +6400,7 @@
         <v>122.8</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A99" s="5">
         <v>42583</v>
       </c>
@@ -6453,7 +6453,7 @@
         <v>86.1</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A100" s="10">
         <v>42552</v>
       </c>
@@ -6506,7 +6506,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A101" s="5">
         <v>42522</v>
       </c>
@@ -6559,7 +6559,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A102" s="10">
         <v>42491</v>
       </c>
@@ -6612,7 +6612,7 @@
         <v>210.6</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A103" s="5">
         <v>42461</v>
       </c>
@@ -6665,7 +6665,7 @@
         <v>139.4</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A104" s="10">
         <v>42430</v>
       </c>
@@ -6718,7 +6718,7 @@
         <v>80.8</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A105" s="5">
         <v>42401</v>
       </c>
@@ -6771,7 +6771,7 @@
         <v>72.7</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A106" s="10">
         <v>42370</v>
       </c>
@@ -6824,7 +6824,7 @@
         <v>309.10000000000002</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A107" s="5">
         <v>42339</v>
       </c>
@@ -6877,7 +6877,7 @@
         <v>1075.3</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A108" s="10">
         <v>42309</v>
       </c>
@@ -6930,7 +6930,7 @@
         <v>1040.5999999999999</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A109" s="5">
         <v>42278</v>
       </c>
@@ -6983,7 +6983,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A110" s="10">
         <v>42248</v>
       </c>
@@ -7036,7 +7036,7 @@
         <v>1050.9000000000001</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A111" s="5">
         <v>42217</v>
       </c>
@@ -7089,7 +7089,7 @@
         <v>1097.7</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A112" s="10">
         <v>42186</v>
       </c>
@@ -7142,7 +7142,7 @@
         <v>419.9</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A113" s="5">
         <v>42156</v>
       </c>
@@ -7195,7 +7195,7 @@
         <v>569.4</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A114" s="10">
         <v>42125</v>
       </c>
@@ -7248,7 +7248,7 @@
         <v>542.29999999999995</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A115" s="5">
         <v>42095</v>
       </c>
@@ -7301,7 +7301,7 @@
         <v>358.1</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A116" s="10">
         <v>42064</v>
       </c>
@@ -7354,7 +7354,7 @@
         <v>535.70000000000005</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A117" s="5">
         <v>42036</v>
       </c>
@@ -7407,7 +7407,7 @@
         <v>562.9</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A118" s="10">
         <v>42005</v>
       </c>
@@ -7460,7 +7460,7 @@
         <v>-21.5</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A119" s="5">
         <v>41974</v>
       </c>
@@ -7513,7 +7513,7 @@
         <v>-45.7</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A120" s="10">
         <v>41944</v>
       </c>
@@ -7566,7 +7566,7 @@
         <v>-49.1</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A121" s="5">
         <v>41913</v>
       </c>
@@ -7619,7 +7619,7 @@
         <v>-49.8</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A122" s="10">
         <v>41883</v>
       </c>
@@ -7672,7 +7672,7 @@
         <v>-41.4</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A123" s="5">
         <v>41852</v>
       </c>
@@ -7725,7 +7725,7 @@
         <v>-44.7</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A124" s="10">
         <v>41821</v>
       </c>
@@ -7778,7 +7778,7 @@
         <v>-48.2</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A125" s="5">
         <v>41791</v>
       </c>
@@ -7831,7 +7831,7 @@
         <v>-58</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A126" s="10">
         <v>41760</v>
       </c>
@@ -7884,7 +7884,7 @@
         <v>-58.4</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A127" s="5">
         <v>41730</v>
       </c>
@@ -7937,652 +7937,652 @@
         <v>-62.4</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A128" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A129" s="5">
         <v>45444</v>
       </c>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A130" s="10">
         <v>45413</v>
       </c>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A131" s="5">
         <v>45383</v>
       </c>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A132" s="10">
         <v>45352</v>
       </c>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A133" s="5">
         <v>45323</v>
       </c>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A134" s="10">
         <v>45292</v>
       </c>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A135" s="5">
         <v>45261</v>
       </c>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A136" s="10">
         <v>45231</v>
       </c>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A137" s="5">
         <v>45200</v>
       </c>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A138" s="10">
         <v>45170</v>
       </c>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A139" s="5">
         <v>45139</v>
       </c>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A140" s="10">
         <v>45108</v>
       </c>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A141" s="5">
         <v>45078</v>
       </c>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A142" s="10">
         <v>45047</v>
       </c>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A143" s="5">
         <v>45017</v>
       </c>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A144" s="10">
         <v>44986</v>
       </c>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A145" s="5">
         <v>44958</v>
       </c>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A146" s="10">
         <v>44927</v>
       </c>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A147" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A148" s="5">
         <v>44896</v>
       </c>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A149" s="10">
         <v>44866</v>
       </c>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A150" s="5">
         <v>44835</v>
       </c>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A151" s="10">
         <v>44805</v>
       </c>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A152" s="5">
         <v>44774</v>
       </c>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A153" s="10">
         <v>44743</v>
       </c>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A154" s="5">
         <v>44713</v>
       </c>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A155" s="10">
         <v>44682</v>
       </c>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A156" s="5">
         <v>44652</v>
       </c>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A157" s="10">
         <v>44621</v>
       </c>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A158" s="5">
         <v>44593</v>
       </c>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A159" s="10">
         <v>44562</v>
       </c>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A160" s="5">
         <v>44531</v>
       </c>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A161" s="10">
         <v>44501</v>
       </c>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A162" s="5">
         <v>44470</v>
       </c>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A163" s="10">
         <v>44440</v>
       </c>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A164" s="5">
         <v>44409</v>
       </c>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A165" s="10">
         <v>44378</v>
       </c>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A166" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A167" s="5">
         <v>44348</v>
       </c>
     </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A168" s="10">
         <v>44317</v>
       </c>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A169" s="5">
         <v>44287</v>
       </c>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A170" s="10">
         <v>44256</v>
       </c>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A171" s="5">
         <v>44228</v>
       </c>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A172" s="10">
         <v>44197</v>
       </c>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A173" s="5">
         <v>44166</v>
       </c>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A174" s="10">
         <v>44136</v>
       </c>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A175" s="5">
         <v>44105</v>
       </c>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A176" s="10">
         <v>44075</v>
       </c>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A177" s="5">
         <v>44044</v>
       </c>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A178" s="10">
         <v>44013</v>
       </c>
     </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A179" s="5">
         <v>43983</v>
       </c>
     </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A180" s="10">
         <v>43952</v>
       </c>
     </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A181" s="5">
         <v>43922</v>
       </c>
     </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A182" s="10">
         <v>43891</v>
       </c>
     </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A183" s="5">
         <v>43862</v>
       </c>
     </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A184" s="10">
         <v>43831</v>
       </c>
     </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A185" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A186" s="5">
         <v>43800</v>
       </c>
     </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A187" s="10">
         <v>43770</v>
       </c>
     </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A188" s="5">
         <v>43739</v>
       </c>
     </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A189" s="10">
         <v>43709</v>
       </c>
     </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A190" s="5">
         <v>43678</v>
       </c>
     </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A191" s="10">
         <v>43647</v>
       </c>
     </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A192" s="5">
         <v>43617</v>
       </c>
     </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A193" s="10">
         <v>43586</v>
       </c>
     </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A194" s="5">
         <v>43556</v>
       </c>
     </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A195" s="10">
         <v>43525</v>
       </c>
     </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A196" s="5">
         <v>43497</v>
       </c>
     </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A197" s="10">
         <v>43466</v>
       </c>
     </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A198" s="5">
         <v>43435</v>
       </c>
     </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A199" s="10">
         <v>43405</v>
       </c>
     </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A200" s="5">
         <v>43374</v>
       </c>
     </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A201" s="10">
         <v>43344</v>
       </c>
     </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A202" s="5">
         <v>43313</v>
       </c>
     </row>
-    <row r="203" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A203" s="10">
         <v>43282</v>
       </c>
     </row>
-    <row r="204" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A204" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A205" s="5">
         <v>43252</v>
       </c>
     </row>
-    <row r="206" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A206" s="10">
         <v>43221</v>
       </c>
     </row>
-    <row r="207" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A207" s="5">
         <v>43191</v>
       </c>
     </row>
-    <row r="208" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A208" s="10">
         <v>43160</v>
       </c>
     </row>
-    <row r="209" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A209" s="5">
         <v>43132</v>
       </c>
     </row>
-    <row r="210" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A210" s="10">
         <v>43101</v>
       </c>
     </row>
-    <row r="211" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A211" s="5">
         <v>43070</v>
       </c>
     </row>
-    <row r="212" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A212" s="10">
         <v>43040</v>
       </c>
     </row>
-    <row r="213" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A213" s="5">
         <v>43009</v>
       </c>
     </row>
-    <row r="214" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A214" s="10">
         <v>42979</v>
       </c>
     </row>
-    <row r="215" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A215" s="5">
         <v>42948</v>
       </c>
     </row>
-    <row r="216" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A216" s="10">
         <v>42917</v>
       </c>
     </row>
-    <row r="217" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A217" s="5">
         <v>42887</v>
       </c>
     </row>
-    <row r="218" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A218" s="10">
         <v>42856</v>
       </c>
     </row>
-    <row r="219" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="219" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A219" s="5">
         <v>42826</v>
       </c>
     </row>
-    <row r="220" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A220" s="10">
         <v>42795</v>
       </c>
     </row>
-    <row r="221" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A221" s="5">
         <v>42767</v>
       </c>
     </row>
-    <row r="222" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A222" s="10">
         <v>42736</v>
       </c>
     </row>
-    <row r="223" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A223" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A224" s="5">
         <v>42705</v>
       </c>
     </row>
-    <row r="225" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A225" s="10">
         <v>42675</v>
       </c>
     </row>
-    <row r="226" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A226" s="5">
         <v>42644</v>
       </c>
     </row>
-    <row r="227" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A227" s="10">
         <v>42614</v>
       </c>
     </row>
-    <row r="228" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A228" s="5">
         <v>42583</v>
       </c>
     </row>
-    <row r="229" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A229" s="10">
         <v>42552</v>
       </c>
     </row>
-    <row r="230" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A230" s="5">
         <v>42522</v>
       </c>
     </row>
-    <row r="231" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="231" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A231" s="10">
         <v>42491</v>
       </c>
     </row>
-    <row r="232" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A232" s="5">
         <v>42461</v>
       </c>
     </row>
-    <row r="233" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A233" s="10">
         <v>42430</v>
       </c>
     </row>
-    <row r="234" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="234" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A234" s="5">
         <v>42401</v>
       </c>
     </row>
-    <row r="235" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="235" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A235" s="10">
         <v>42370</v>
       </c>
     </row>
-    <row r="236" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="236" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A236" s="5">
         <v>42339</v>
       </c>
     </row>
-    <row r="237" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A237" s="10">
         <v>42309</v>
       </c>
     </row>
-    <row r="238" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="238" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A238" s="5">
         <v>42278</v>
       </c>
     </row>
-    <row r="239" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="239" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A239" s="10">
         <v>42248</v>
       </c>
     </row>
-    <row r="240" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="240" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A240" s="5">
         <v>42217</v>
       </c>
     </row>
-    <row r="241" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="241" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A241" s="10">
         <v>42186</v>
       </c>
     </row>
-    <row r="242" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="242" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A242" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="243" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A243" s="5">
         <v>42156</v>
       </c>
     </row>
-    <row r="244" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="244" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A244" s="10">
         <v>42125</v>
       </c>
     </row>
-    <row r="245" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="245" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A245" s="5">
         <v>42095</v>
       </c>
     </row>
-    <row r="246" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="246" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A246" s="10">
         <v>42064</v>
       </c>
     </row>
-    <row r="247" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="247" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A247" s="5">
         <v>42036</v>
       </c>
     </row>
-    <row r="248" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="248" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A248" s="10">
         <v>42005</v>
       </c>
     </row>
-    <row r="249" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="249" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A249" s="5">
         <v>41974</v>
       </c>
     </row>
-    <row r="250" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="250" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A250" s="10">
         <v>41944</v>
       </c>
     </row>
-    <row r="251" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="251" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A251" s="5">
         <v>41913</v>
       </c>
     </row>
-    <row r="252" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="252" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A252" s="10">
         <v>41883</v>
       </c>
     </row>
-    <row r="253" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="253" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A253" s="5">
         <v>41852</v>
       </c>
     </row>
-    <row r="254" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="254" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A254" s="10">
         <v>41821</v>
       </c>
     </row>
-    <row r="255" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="255" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A255" s="5">
         <v>41791</v>
       </c>
     </row>
-    <row r="256" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="256" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A256" s="10">
         <v>41760</v>
       </c>
     </row>
-    <row r="257" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="257" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A257" s="5">
         <v>41730</v>
       </c>
